--- a/Data/Home/LivingRoom.AirQuality.xlsx
+++ b/Data/Home/LivingRoom.AirQuality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709281596</v>
+        <v>1711842102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709285345</v>
+        <v>1711851442</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709286219</v>
+        <v>1711852236</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709290698</v>
+        <v>1711873280</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709291587</v>
+        <v>1711874234</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709225467</v>
+        <v>1711885086</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709226301</v>
+        <v>1711886077</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709245767</v>
+        <v>1711888738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709246465</v>
+        <v>1711889605</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709333286</v>
+        <v>1711894425</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709334117</v>
+        <v>1711895202</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709338909</v>
+        <v>1711930678</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709339764</v>
+        <v>1711931458</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709348686</v>
+        <v>1711936690</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709349514</v>
+        <v>1711937484</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709359161</v>
+        <v>1712019152</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709359967</v>
+        <v>1712020099</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709366059</v>
+        <v>1712023009</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709366829</v>
+        <v>1712023954</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709400983</v>
+        <v>1712028357</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709401697</v>
+        <v>1712029169</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709422605</v>
+        <v>1712106291</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709423491</v>
+        <v>1712107029</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709429902</v>
+        <v>1712134122</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709430742</v>
+        <v>1712134975</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709444761</v>
+        <v>1712139227</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1331,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709445585</v>
+        <v>1712140008</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709453377</v>
+        <v>1712147724</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709454154</v>
+        <v>1712148521</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709464799</v>
+        <v>1712280523</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709465512</v>
+        <v>1712281312</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709507774</v>
+        <v>1712299850</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709508638</v>
+        <v>1712300823</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709514240</v>
+        <v>1712304724</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709515043</v>
+        <v>1712305592</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709532408</v>
+        <v>1712313652</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709533144</v>
+        <v>1712314443</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709617357</v>
+        <v>1712379112</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709618205</v>
+        <v>1712379965</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709626181</v>
+        <v>1712389802</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709626920</v>
+        <v>1712390787</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709690660</v>
+        <v>1712394472</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709691537</v>
+        <v>1712395341</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709696639</v>
+        <v>1712402114</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709697429</v>
+        <v>1712402916</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709708823</v>
+        <v>1712466232</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709709667</v>
+        <v>1712467183</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709722985</v>
+        <v>1712476607</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709723717</v>
+        <v>1712477622</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709776065</v>
+        <v>1712481218</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709776783</v>
+        <v>1712482109</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709781551</v>
+        <v>1712491285</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709782295</v>
+        <v>1712492069</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709791780</v>
+        <v>1712500847</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709792541</v>
+        <v>1712501738</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709798621</v>
+        <v>1712507734</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709799343</v>
+        <v>1712508529</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709848641</v>
+        <v>1712538440</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709849318</v>
+        <v>1712539420</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709854221</v>
+        <v>1712542669</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709854987</v>
+        <v>1712543551</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709859898</v>
+        <v>1712553126</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709860674</v>
+        <v>1712553978</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709866999</v>
+        <v>1712558158</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709867866</v>
+        <v>1712559065</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2618,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709870412</v>
+        <v>1712565008</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709871282</v>
+        <v>1712565937</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709873837</v>
+        <v>1712569431</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709874761</v>
+        <v>1712570299</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2750,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709878288</v>
+        <v>1712576841</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2783,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709879117</v>
+        <v>1712577612</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709887170</v>
+        <v>1712624498</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709887929</v>
+        <v>1712625488</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2882,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709939255</v>
+        <v>1712629046</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2915,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709940084</v>
+        <v>1712629926</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709947637</v>
+        <v>1712642881</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2981,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709948469</v>
+        <v>1712643769</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3014,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709963573</v>
+        <v>1712651238</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709964394</v>
+        <v>1712652100</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709970284</v>
+        <v>1712660081</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3113,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709971080</v>
+        <v>1712660878</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709980888</v>
+        <v>1712732666</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709981632</v>
+        <v>1712733636</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710048328</v>
+        <v>1712737516</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710049157</v>
+        <v>1712738410</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3278,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710055312</v>
+        <v>1712749457</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710056228</v>
+        <v>1712750266</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710062189</v>
+        <v>1712800315</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710063019</v>
+        <v>1712801121</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710091699</v>
+        <v>1712815037</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710092423</v>
+        <v>1712816002</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710135481</v>
+        <v>1712819825</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710136354</v>
+        <v>1712820691</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710146759</v>
+        <v>1712827538</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710147612</v>
+        <v>1712828334</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710195663</v>
+        <v>1712883546</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710196386</v>
+        <v>1712884539</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710217151</v>
+        <v>1712887885</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710218040</v>
+        <v>1712888754</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710227843</v>
+        <v>1712895738</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710228564</v>
+        <v>1712896544</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710239025</v>
+        <v>1712905250</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710239818</v>
+        <v>1712906050</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710246305</v>
+        <v>1712913524</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710259776</v>
+        <v>1712914339</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710265891</v>
+        <v>1712923202</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710266656</v>
+        <v>1712924184</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4004,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710309338</v>
+        <v>1712927428</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4037,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710310160</v>
+        <v>1712928324</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710318847</v>
+        <v>1712940543</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4103,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710319661</v>
+        <v>1712941330</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4136,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710327173</v>
+        <v>1712995948</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710327914</v>
+        <v>1712996914</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710346741</v>
+        <v>1713000549</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4235,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710347552</v>
+        <v>1713001428</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4268,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710353291</v>
+        <v>1713013119</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710354079</v>
+        <v>1713013911</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710365833</v>
+        <v>1713025973</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710366602</v>
+        <v>1713026769</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710388903</v>
+        <v>1713069023</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710389664</v>
+        <v>1713070007</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710397117</v>
+        <v>1713074088</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710398013</v>
+        <v>1713074902</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710404206</v>
+        <v>1713087127</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710404977</v>
+        <v>1713088107</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4598,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710433330</v>
+        <v>1713091636</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710434137</v>
+        <v>1713092530</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710441715</v>
+        <v>1713099158</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710442467</v>
+        <v>1713100016</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4730,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710459520</v>
+        <v>1713104700</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4763,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710460498</v>
+        <v>1713105500</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710463710</v>
+        <v>1713115524</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4829,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710464622</v>
+        <v>1713116395</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710468893</v>
+        <v>1713114894</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710469736</v>
+        <v>1713115693</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710480043</v>
+        <v>1713142172</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710480802</v>
+        <v>1713143045</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +4994,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710490065</v>
+        <v>1713149436</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710490770</v>
+        <v>1713150239</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710501197</v>
+        <v>1713163045</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5093,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710501968</v>
+        <v>1713163716</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5126,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710632946</v>
+        <v>1713168577</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5159,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710633854</v>
+        <v>1713169322</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5192,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710640879</v>
+        <v>1713172487</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710641734</v>
+        <v>1713173355</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5258,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710654824</v>
+        <v>1713176440</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5291,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710655698</v>
+        <v>1713177245</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5324,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710669028</v>
+        <v>1713186989</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5357,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710669890</v>
+        <v>1713187722</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5390,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710691448</v>
+        <v>1713248462</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5423,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710692278</v>
+        <v>1713249254</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5456,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710696025</v>
+        <v>1713261768</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5489,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710696869</v>
+        <v>1713262646</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5522,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710701267</v>
+        <v>1713269986</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5555,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710702110</v>
+        <v>1713270772</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5588,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710706476</v>
+        <v>1713316877</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5621,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710707358</v>
+        <v>1713317814</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5654,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710737442</v>
+        <v>1713321044</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5687,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710738296</v>
+        <v>1713321917</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5720,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710748268</v>
+        <v>1713328726</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5753,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5772,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710749146</v>
+        <v>1713329495</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5786,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5805,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710779705</v>
+        <v>1713337912</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5819,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5838,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710780418</v>
+        <v>1713338637</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5852,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5871,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710805059</v>
+        <v>1713348269</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5885,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5904,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710805993</v>
+        <v>1713348972</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5918,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5937,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710811902</v>
+        <v>1713358046</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +5951,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5970,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710812800</v>
+        <v>1713358836</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +5984,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6003,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710831670</v>
+        <v>1713427713</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6017,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6036,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710832504</v>
+        <v>1713428591</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6050,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6069,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710839713</v>
+        <v>1713436547</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6083,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6102,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710840597</v>
+        <v>1713437423</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6116,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6135,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710869938</v>
+        <v>1713443771</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6149,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6168,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710870688</v>
+        <v>1713444558</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6182,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710904248</v>
+        <v>1713488945</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6215,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6234,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710905024</v>
+        <v>1713489820</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6248,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6267,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710913006</v>
+        <v>1713494114</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6281,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6300,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710913855</v>
+        <v>1713494894</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6314,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6333,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710923374</v>
+        <v>1713520140</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6347,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6366,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710924214</v>
+        <v>1713520931</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6380,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6399,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710933924</v>
+        <v>1713524154</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6413,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6432,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710934782</v>
+        <v>1713525028</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6446,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6465,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710954637</v>
+        <v>1713529639</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6479,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6498,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710955472</v>
+        <v>1713530408</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6512,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6531,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710963562</v>
+        <v>1713588103</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6545,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6564,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710964301</v>
+        <v>1713589113</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6578,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6597,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710991194</v>
+        <v>1713591578</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6611,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6630,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710992127</v>
+        <v>1713592525</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6644,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6663,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711000250</v>
+        <v>1713596764</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6677,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6696,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711001149</v>
+        <v>1713597564</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6710,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6729,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711009181</v>
+        <v>1713604975</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6743,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6762,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711010016</v>
+        <v>1713605868</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6776,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6795,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711020913</v>
+        <v>1713613858</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6809,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6828,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711037422</v>
+        <v>1713614646</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6842,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6861,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711042628</v>
+        <v>1713632969</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6875,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6894,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711043505</v>
+        <v>1713633761</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +6908,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6927,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711046911</v>
+        <v>1713631845</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +6941,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +6960,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711047752</v>
+        <v>1713632566</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +6974,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +6993,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711052130</v>
+        <v>1713639457</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7007,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7026,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711053031</v>
+        <v>1713640127</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7040,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7059,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711057511</v>
+        <v>1713675430</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7073,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7092,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711058367</v>
+        <v>1713676153</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7106,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7125,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711096402</v>
+        <v>1713682436</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7139,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7158,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711097190</v>
+        <v>1713683247</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7172,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7191,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711132784</v>
+        <v>1713686416</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7205,7 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7224,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711133575</v>
+        <v>1713687214</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7238,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7257,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711168340</v>
+        <v>1713690905</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7271,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7290,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711169152</v>
+        <v>1713691627</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7304,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7323,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711177088</v>
+        <v>1713702555</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7337,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7356,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711177888</v>
+        <v>1713703224</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7370,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7389,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711186290</v>
+        <v>1713714999</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7403,7 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7422,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711187070</v>
+        <v>1713715535</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7436,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7455,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711238092</v>
+        <v>1713719234</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7469,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7488,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711238928</v>
+        <v>1713719947</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7502,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7521,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711245642</v>
+        <v>1713726899</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7535,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7554,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711246487</v>
+        <v>1713727558</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7568,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7587,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711261875</v>
+        <v>1713834442</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,6 +7601,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7620,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711262804</v>
+        <v>1713835415</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7634,7 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7653,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711268422</v>
+        <v>1713839002</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7667,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7686,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711269276</v>
+        <v>1713839878</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7477,6 +7700,7 @@
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7719,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711278626</v>
+        <v>1713847448</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7509,6 +7733,7 @@
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7752,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711279361</v>
+        <v>1713848243</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7766,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7785,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711347055</v>
+        <v>1713920318</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7573,6 +7799,7 @@
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7818,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711347961</v>
+        <v>1713921280</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +7832,7 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7851,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711355177</v>
+        <v>1713924882</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7865,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7884,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711356063</v>
+        <v>1713925767</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7669,6 +7898,7 @@
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +7917,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711360932</v>
+        <v>1713933776</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7701,6 +7931,7 @@
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +7950,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711361741</v>
+        <v>1713934500</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +7964,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +7983,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711368845</v>
+        <v>1713950459</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7765,6 +7997,7 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8016,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711369501</v>
+        <v>1713951338</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7797,6 +8030,7 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8049,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711416243</v>
+        <v>1713959695</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7829,6 +8063,7 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8082,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711417111</v>
+        <v>1713960488</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7861,6 +8096,7 @@
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8115,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711421268</v>
+        <v>1714008056</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7893,6 +8129,7 @@
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8148,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711422006</v>
+        <v>1714009023</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8162,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8181,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711442714</v>
+        <v>1714012691</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7957,6 +8195,7 @@
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8214,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711443563</v>
+        <v>1714013568</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7989,6 +8228,7 @@
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8247,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711446611</v>
+        <v>1714025920</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8261,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8280,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711447469</v>
+        <v>1714026684</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8053,6 +8294,7 @@
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8313,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711450397</v>
+        <v>1714038356</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8085,6 +8327,7 @@
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8346,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711451304</v>
+        <v>1714039212</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8360,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8379,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711454419</v>
+        <v>1714042533</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8149,6 +8393,7 @@
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8412,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711455258</v>
+        <v>1714043390</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8426,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8445,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711458931</v>
+        <v>1714049015</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8213,6 +8459,7 @@
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8478,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711459702</v>
+        <v>1714049782</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8245,6 +8492,7 @@
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8511,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711521562</v>
+        <v>1714092531</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8525,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8544,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711522238</v>
+        <v>1714093362</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8558,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8577,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711530246</v>
+        <v>1714100161</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8591,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8610,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711531101</v>
+        <v>1714100957</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8624,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8643,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711539612</v>
+        <v>1714114816</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8657,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8676,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711540356</v>
+        <v>1714115785</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8437,6 +8690,7 @@
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8709,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711613968</v>
+        <v>1714124799</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8723,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8742,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711614862</v>
+        <v>1714125652</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8756,7 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8775,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711618426</v>
+        <v>1714133888</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8533,6 +8789,7 @@
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8808,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711619319</v>
+        <v>1714134651</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8565,6 +8822,7 @@
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8841,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711623242</v>
+        <v>1714201677</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8855,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +8874,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711624044</v>
+        <v>1714202447</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8629,6 +8888,7 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +8907,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711632511</v>
+        <v>1714209530</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8661,6 +8921,7 @@
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +8940,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711633198</v>
+        <v>1714210401</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +8954,733 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1714218436</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1714219233</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1714238342</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1714239321</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1714234475</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1714235491</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1714238935</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1714239809</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1714247038</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1714247762</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1714280913</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1714281799</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1714285841</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1714286630</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1714293394</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1714294282</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1714303624</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1714304635</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1714307449</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1714308320</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1714313267</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1714314046</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
